--- a/src/main/resources/Organizational_DeskReview_Field_Values.xlsx
+++ b/src/main/resources/Organizational_DeskReview_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B164733-7515-4E55-A531-43CC3255CA75}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C549426-EBDA-47CA-BD97-FB7828A38ECB}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="6" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>

--- a/src/main/resources/Organizational_DeskReview_Field_Values.xlsx
+++ b/src/main/resources/Organizational_DeskReview_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21629"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21727"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C549426-EBDA-47CA-BD97-FB7828A38ECB}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53DA0360-8FF9-43CA-9C55-A0A6EE758A3D}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="6" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="5" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -18,9 +18,10 @@
     <sheet name="Award" sheetId="9" r:id="rId3"/>
     <sheet name="Sheet1" sheetId="4" r:id="rId4"/>
     <sheet name="Edition" sheetId="3" r:id="rId5"/>
-    <sheet name="Program" sheetId="6" r:id="rId6"/>
-    <sheet name="Fiscal" sheetId="7" r:id="rId7"/>
-    <sheet name="Form Fields" sheetId="5" r:id="rId8"/>
+    <sheet name="Edition1" sheetId="10" r:id="rId6"/>
+    <sheet name="Program" sheetId="6" r:id="rId7"/>
+    <sheet name="Fiscal" sheetId="7" r:id="rId8"/>
+    <sheet name="Form Fields" sheetId="5" r:id="rId9"/>
   </sheets>
   <calcPr calcId="179017"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="50">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -918,6 +919,88 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{139F1479-2E59-4670-8557-FD1A600D9DD9}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.77734375" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{172EB3BB-E440-4D9F-AB45-F40BA5013EFF}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -988,7 +1071,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54C0A2D9-C8FF-4F2E-9357-11D1A04AB716}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1059,7 +1142,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F8298A-0165-44BF-9061-10BEE0A93A27}">
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/src/main/resources/Organizational_DeskReview_Field_Values.xlsx
+++ b/src/main/resources/Organizational_DeskReview_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53DA0360-8FF9-43CA-9C55-A0A6EE758A3D}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{356FBB87-902C-4690-AF5E-363BF286544E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="5" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="51">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -183,6 +183,9 @@
   </si>
   <si>
     <t>Application</t>
+  </si>
+  <si>
+    <t>Automation spi</t>
   </si>
 </sst>
 </file>
@@ -542,13 +545,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27F20A35-8E6F-4015-873C-76781E4C62A4}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -559,7 +562,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -570,7 +573,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -578,10 +581,10 @@
         <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -592,7 +595,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -611,15 +614,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F7BC2C8-C330-4CF5-B350-FDF7466963B4}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.77734375" style="1"/>
-    <col min="2" max="2" width="20.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.77734375" style="1"/>
+    <col min="1" max="1" width="8.7109375" style="1"/>
+    <col min="2" max="2" width="20.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -630,7 +633,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -641,7 +644,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -652,7 +655,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -663,7 +666,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -682,15 +685,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{661F5711-50C5-4AD1-966A-EEB6DD06A5CB}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.77734375" style="1"/>
-    <col min="2" max="2" width="20.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.77734375" style="1"/>
+    <col min="1" max="1" width="8.7109375" style="1"/>
+    <col min="2" max="2" width="20.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -701,7 +704,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -712,7 +715,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -723,7 +726,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -734,7 +737,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -753,12 +756,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFC7A54C-E16D-458B-92CE-DB4DE5E21708}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -766,7 +769,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -774,7 +777,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -782,7 +785,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -790,22 +793,22 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
         <v>27</v>
       </c>
@@ -818,14 +821,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4969FD67-2E2F-4920-8A24-9B3F6A7CB976}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -836,7 +839,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>13</v>
       </c>
@@ -847,7 +850,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -858,7 +861,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
@@ -869,7 +872,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
@@ -880,7 +883,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -891,7 +894,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
@@ -902,7 +905,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
@@ -921,15 +924,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{139F1479-2E59-4670-8557-FD1A600D9DD9}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.77734375" style="1"/>
+    <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -940,7 +943,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>13</v>
       </c>
@@ -951,7 +954,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -962,7 +965,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
@@ -973,7 +976,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
@@ -984,7 +987,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -1003,15 +1006,15 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{172EB3BB-E440-4D9F-AB45-F40BA5013EFF}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.77734375" style="1"/>
-    <col min="2" max="2" width="20.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.77734375" style="1"/>
+    <col min="1" max="1" width="8.7109375" style="1"/>
+    <col min="2" max="2" width="20.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1022,7 +1025,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1033,7 +1036,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1044,7 +1047,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -1055,7 +1058,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -1074,15 +1077,15 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54C0A2D9-C8FF-4F2E-9357-11D1A04AB716}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.77734375" style="1"/>
-    <col min="2" max="2" width="20.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.77734375" style="1"/>
+    <col min="1" max="1" width="8.7109375" style="1"/>
+    <col min="2" max="2" width="20.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1093,7 +1096,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1104,7 +1107,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1115,7 +1118,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -1126,7 +1129,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -1145,14 +1148,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F8298A-0165-44BF-9061-10BEE0A93A27}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.33203125" customWidth="1"/>
-    <col min="3" max="3" width="100.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.28515625" customWidth="1"/>
+    <col min="3" max="3" width="100.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1163,7 +1166,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1174,7 +1177,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1185,7 +1188,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -1196,7 +1199,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -1207,7 +1210,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -1218,7 +1221,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
@@ -1229,7 +1232,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
@@ -1240,7 +1243,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1251,7 +1254,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>

--- a/src/main/resources/Organizational_DeskReview_Field_Values.xlsx
+++ b/src/main/resources/Organizational_DeskReview_Field_Values.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{356FBB87-902C-4690-AF5E-363BF286544E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18B6EFBE-23AC-43D3-94AB-5285161DE5C1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="8" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="50">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -183,9 +183,6 @@
   </si>
   <si>
     <t>Application</t>
-  </si>
-  <si>
-    <t>Automation spi</t>
   </si>
 </sst>
 </file>
@@ -545,13 +542,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27F20A35-8E6F-4015-873C-76781E4C62A4}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -562,7 +559,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -573,7 +570,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -581,10 +578,10 @@
         <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -595,7 +592,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -614,15 +611,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F7BC2C8-C330-4CF5-B350-FDF7466963B4}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" style="1"/>
-    <col min="2" max="2" width="20.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.7109375" style="1"/>
+    <col min="1" max="1" width="8.6640625" style="1"/>
+    <col min="2" max="2" width="20.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -633,7 +630,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -644,7 +641,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -655,7 +652,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -666,7 +663,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -685,15 +682,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{661F5711-50C5-4AD1-966A-EEB6DD06A5CB}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" style="1"/>
-    <col min="2" max="2" width="20.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.7109375" style="1"/>
+    <col min="1" max="1" width="8.6640625" style="1"/>
+    <col min="2" max="2" width="20.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -704,7 +701,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -715,7 +712,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -726,7 +723,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -737,7 +734,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -756,12 +753,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFC7A54C-E16D-458B-92CE-DB4DE5E21708}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -769,7 +766,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -777,7 +774,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -785,7 +782,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -793,22 +790,22 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
         <v>27</v>
       </c>
@@ -821,14 +818,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4969FD67-2E2F-4920-8A24-9B3F6A7CB976}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -839,7 +836,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>13</v>
       </c>
@@ -850,7 +847,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -861,7 +858,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
@@ -872,7 +869,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
@@ -883,7 +880,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -894,7 +891,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
@@ -905,7 +902,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
@@ -924,15 +921,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{139F1479-2E59-4670-8557-FD1A600D9DD9}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.7109375" style="1"/>
+    <col min="1" max="1" width="8.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -943,7 +940,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>13</v>
       </c>
@@ -954,7 +951,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -965,7 +962,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
@@ -976,7 +973,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
@@ -987,7 +984,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -1006,15 +1003,15 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{172EB3BB-E440-4D9F-AB45-F40BA5013EFF}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" style="1"/>
-    <col min="2" max="2" width="20.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.7109375" style="1"/>
+    <col min="1" max="1" width="8.6640625" style="1"/>
+    <col min="2" max="2" width="20.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1025,7 +1022,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1036,7 +1033,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1047,7 +1044,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -1058,7 +1055,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -1077,15 +1074,15 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54C0A2D9-C8FF-4F2E-9357-11D1A04AB716}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" style="1"/>
-    <col min="2" max="2" width="20.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.7109375" style="1"/>
+    <col min="1" max="1" width="8.6640625" style="1"/>
+    <col min="2" max="2" width="20.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1096,7 +1093,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1107,7 +1104,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1118,7 +1115,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -1129,7 +1126,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -1148,14 +1145,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F8298A-0165-44BF-9061-10BEE0A93A27}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.28515625" customWidth="1"/>
-    <col min="3" max="3" width="100.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.33203125" customWidth="1"/>
+    <col min="3" max="3" width="100.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1166,7 +1163,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1177,7 +1174,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1188,7 +1185,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -1199,7 +1196,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -1210,7 +1207,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -1221,7 +1218,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
@@ -1232,7 +1229,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
@@ -1243,7 +1240,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1254,7 +1251,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>

--- a/src/main/resources/Organizational_DeskReview_Field_Values.xlsx
+++ b/src/main/resources/Organizational_DeskReview_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18B6EFBE-23AC-43D3-94AB-5285161DE5C1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA620691-8A42-4375-9F1E-FE8DB153FC52}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="8" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="51">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -183,6 +183,9 @@
   </si>
   <si>
     <t>Application</t>
+  </si>
+  <si>
+    <t>Automation Runtime Desk Review Org level</t>
   </si>
 </sst>
 </file>
@@ -567,7 +570,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">

--- a/src/main/resources/Organizational_DeskReview_Field_Values.xlsx
+++ b/src/main/resources/Organizational_DeskReview_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Product\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA620691-8A42-4375-9F1E-FE8DB153FC52}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FC2315C-900F-403B-BCE8-27CE7168B71E}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12570" activeTab="6" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="53">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -186,6 +186,12 @@
   </si>
   <si>
     <t>Automation Runtime Desk Review Org level</t>
+  </si>
+  <si>
+    <t>Fiscal</t>
+  </si>
+  <si>
+    <t>Program</t>
   </si>
 </sst>
 </file>
@@ -545,13 +551,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27F20A35-8E6F-4015-873C-76781E4C62A4}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -562,7 +568,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -573,7 +579,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -584,7 +590,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -595,7 +601,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -614,15 +620,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F7BC2C8-C330-4CF5-B350-FDF7466963B4}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" style="1"/>
-    <col min="2" max="2" width="20.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.6640625" style="1"/>
+    <col min="1" max="1" width="8.7109375" style="1"/>
+    <col min="2" max="2" width="20.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -633,7 +639,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -644,7 +650,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -655,7 +661,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -666,7 +672,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -685,15 +691,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{661F5711-50C5-4AD1-966A-EEB6DD06A5CB}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" style="1"/>
-    <col min="2" max="2" width="20.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.6640625" style="1"/>
+    <col min="1" max="1" width="8.7109375" style="1"/>
+    <col min="2" max="2" width="20.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -704,7 +710,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -715,7 +721,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -726,7 +732,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -737,7 +743,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -756,12 +762,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFC7A54C-E16D-458B-92CE-DB4DE5E21708}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -769,7 +775,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -777,7 +783,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -785,7 +791,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -793,22 +799,22 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
         <v>27</v>
       </c>
@@ -821,14 +827,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4969FD67-2E2F-4920-8A24-9B3F6A7CB976}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -839,7 +845,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>13</v>
       </c>
@@ -850,7 +856,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -861,7 +867,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
@@ -872,7 +878,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
@@ -883,7 +889,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -894,7 +900,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
@@ -905,7 +911,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
@@ -924,15 +930,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{139F1479-2E59-4670-8557-FD1A600D9DD9}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.6640625" style="1"/>
+    <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -943,7 +949,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>13</v>
       </c>
@@ -954,7 +960,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -965,7 +971,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
@@ -976,7 +982,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
@@ -987,7 +993,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -1006,15 +1012,15 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{172EB3BB-E440-4D9F-AB45-F40BA5013EFF}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" style="1"/>
-    <col min="2" max="2" width="20.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.6640625" style="1"/>
+    <col min="1" max="1" width="8.7109375" style="1"/>
+    <col min="2" max="2" width="20.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1025,7 +1031,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1036,7 +1042,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1047,7 +1053,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -1055,10 +1061,10 @@
         <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -1077,15 +1083,15 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54C0A2D9-C8FF-4F2E-9357-11D1A04AB716}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" style="1"/>
-    <col min="2" max="2" width="20.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.6640625" style="1"/>
+    <col min="1" max="1" width="8.7109375" style="1"/>
+    <col min="2" max="2" width="20.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1096,7 +1102,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1107,7 +1113,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1118,7 +1124,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -1126,10 +1132,10 @@
         <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -1148,14 +1154,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F8298A-0165-44BF-9061-10BEE0A93A27}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.33203125" customWidth="1"/>
-    <col min="3" max="3" width="100.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.28515625" customWidth="1"/>
+    <col min="3" max="3" width="100.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1166,7 +1172,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1177,7 +1183,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1188,7 +1194,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -1199,7 +1205,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -1210,7 +1216,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -1221,7 +1227,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
@@ -1232,7 +1238,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
@@ -1243,7 +1249,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1254,7 +1260,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>

--- a/src/main/resources/Organizational_DeskReview_Field_Values.xlsx
+++ b/src/main/resources/Organizational_DeskReview_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Product\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workpace-gov-grants-framework-automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FC2315C-900F-403B-BCE8-27CE7168B71E}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A78FA35-9B7C-4BDF-B484-BE9759C4262F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12570" activeTab="6" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10395" activeTab="2" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="54">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -62,9 +62,6 @@
     <t>GranteePOCContact__c</t>
   </si>
   <si>
-    <t>Automation SPI</t>
-  </si>
-  <si>
     <t>DropDown</t>
   </si>
   <si>
@@ -192,6 +189,12 @@
   </si>
   <si>
     <t>Program</t>
+  </si>
+  <si>
+    <t>Automation SPI3</t>
+  </si>
+  <si>
+    <t>fieldTitle__c</t>
   </si>
 </sst>
 </file>
@@ -551,13 +554,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27F20A35-8E6F-4015-873C-76781E4C62A4}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.46484375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -568,7 +571,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -576,10 +579,10 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -587,29 +590,29 @@
         <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" t="s">
         <v>46</v>
-      </c>
-      <c r="C5" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -620,15 +623,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F7BC2C8-C330-4CF5-B350-FDF7466963B4}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" style="1"/>
-    <col min="2" max="2" width="20.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.7109375" style="1"/>
+    <col min="1" max="1" width="8.73046875" style="1"/>
+    <col min="2" max="2" width="20.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.73046875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.73046875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -639,7 +642,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -647,10 +650,10 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -658,29 +661,29 @@
         <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -691,15 +694,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{661F5711-50C5-4AD1-966A-EEB6DD06A5CB}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" style="1"/>
-    <col min="2" max="2" width="20.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.7109375" style="1"/>
+    <col min="1" max="1" width="8.73046875" style="1"/>
+    <col min="2" max="2" width="20.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.19921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.73046875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -710,18 +713,18 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>53</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -729,29 +732,29 @@
         <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -762,12 +765,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFC7A54C-E16D-458B-92CE-DB4DE5E21708}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.19921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -775,48 +779,48 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B5" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B6" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B7" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B8" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -827,14 +831,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4969FD67-2E2F-4920-8A24-9B3F6A7CB976}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.1328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.1328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -845,81 +849,81 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C2" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="C6" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="1" t="s">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>26</v>
-      </c>
       <c r="C8" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -930,15 +934,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{139F1479-2E59-4670-8557-FD1A600D9DD9}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.7109375" style="1"/>
+    <col min="1" max="1" width="8.73046875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.1328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.1328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.73046875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -949,59 +953,59 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C2" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="C5" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -1012,15 +1016,15 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{172EB3BB-E440-4D9F-AB45-F40BA5013EFF}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" style="1"/>
-    <col min="2" max="2" width="20.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.7109375" style="1"/>
+    <col min="1" max="1" width="8.73046875" style="1"/>
+    <col min="2" max="2" width="20.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.73046875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.73046875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1031,7 +1035,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1039,10 +1043,10 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1050,29 +1054,29 @@
         <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1083,15 +1087,15 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54C0A2D9-C8FF-4F2E-9357-11D1A04AB716}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" style="1"/>
-    <col min="2" max="2" width="20.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.7109375" style="1"/>
+    <col min="1" max="1" width="8.73046875" style="1"/>
+    <col min="2" max="2" width="20.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.73046875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.73046875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1102,7 +1106,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1110,10 +1114,10 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1121,29 +1125,29 @@
         <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1154,14 +1158,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F8298A-0165-44BF-9061-10BEE0A93A27}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.28515625" customWidth="1"/>
-    <col min="3" max="3" width="100.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.265625" customWidth="1"/>
+    <col min="3" max="3" width="100.1328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1172,103 +1176,103 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" t="s">
         <v>28</v>
       </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>30</v>
       </c>
-      <c r="C3" t="s">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>32</v>
       </c>
-      <c r="C4" t="s">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>34</v>
       </c>
-      <c r="C5" t="s">
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>36</v>
       </c>
-      <c r="C6" t="s">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>38</v>
       </c>
-      <c r="C7" t="s">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>40</v>
       </c>
-      <c r="C8" t="s">
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>42</v>
       </c>
-      <c r="C9" t="s">
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>44</v>
-      </c>
-      <c r="C10" t="s">
-        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/Organizational_DeskReview_Field_Values.xlsx
+++ b/src/main/resources/Organizational_DeskReview_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workpace-gov-grants-framework-automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A78FA35-9B7C-4BDF-B484-BE9759C4262F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69C4FE80-E0C7-4340-91C4-8F3DDD432FFF}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10395" activeTab="2" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10395" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>

--- a/src/main/resources/Organizational_DeskReview_Field_Values.xlsx
+++ b/src/main/resources/Organizational_DeskReview_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25028"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workpace-gov-grants-framework-automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69C4FE80-E0C7-4340-91C4-8F3DDD432FFF}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9582B3DC-C297-46D0-981C-ACA6E6B6CDC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10395" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="57">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -77,42 +77,21 @@
     <t>Date</t>
   </si>
   <si>
-    <t>VisitDateandTime__c</t>
-  </si>
-  <si>
-    <t>VisitEndDateTime__c</t>
-  </si>
-  <si>
-    <t>Description__c</t>
-  </si>
-  <si>
     <t>RichText</t>
   </si>
   <si>
     <t>Automation Test description</t>
   </si>
   <si>
-    <t>Pointsdiscussedwithofficials__c</t>
-  </si>
-  <si>
-    <t>SiteVisitPurpose__c</t>
-  </si>
-  <si>
     <t>Dropdown</t>
   </si>
   <si>
     <t>Routine based on monitoring responsibilities</t>
   </si>
   <si>
-    <t>SourceSiteVisit__c</t>
-  </si>
-  <si>
     <t>To fulfill pass-through monitoring responsibilities</t>
   </si>
   <si>
-    <t>SupportingCommentsQuestion1__c</t>
-  </si>
-  <si>
     <t>TextArea</t>
   </si>
   <si>
@@ -179,9 +158,6 @@
     <t>Automation Desk Review Org level</t>
   </si>
   <si>
-    <t>Application</t>
-  </si>
-  <si>
     <t>Automation Runtime Desk Review Org level</t>
   </si>
   <si>
@@ -195,19 +171,58 @@
   </si>
   <si>
     <t>fieldTitle__c</t>
+  </si>
+  <si>
+    <t>fieldVisitDateandTime__c</t>
+  </si>
+  <si>
+    <t>fieldVisitEndDateTime__c</t>
+  </si>
+  <si>
+    <t>fieldDescription__c</t>
+  </si>
+  <si>
+    <t>fieldPointsdiscussedwithofficials__c</t>
+  </si>
+  <si>
+    <t>fieldSiteVisitPurpose__c</t>
+  </si>
+  <si>
+    <t>fieldSourceSiteVisit__c</t>
+  </si>
+  <si>
+    <t>fieldSupportingCommentsQuestion1__c</t>
+  </si>
+  <si>
+    <t>fieldGranteePOCContact__c</t>
+  </si>
+  <si>
+    <t>fieldSiteVisitType__c</t>
+  </si>
+  <si>
+    <t>fieldMonitoringType__c</t>
+  </si>
+  <si>
+    <t>Other</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF202124"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -230,7 +245,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -239,6 +254,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -554,13 +570,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27F20A35-8E6F-4015-873C-76781E4C62A4}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="20.3984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.46484375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -571,7 +587,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -579,10 +595,10 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -590,10 +606,10 @@
         <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -604,15 +620,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C5" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -623,15 +639,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F7BC2C8-C330-4CF5-B350-FDF7466963B4}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.73046875" style="1"/>
-    <col min="2" max="2" width="20.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.73046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.73046875" style="1"/>
+    <col min="1" max="1" width="8.7109375" style="1"/>
+    <col min="2" max="2" width="20.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -642,48 +658,48 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>6</v>
+      <c r="B2" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
+      <c r="B3" s="4" t="s">
+        <v>53</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>10</v>
+      <c r="B4" s="4" t="s">
+        <v>55</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>48</v>
+      <c r="B5" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -694,15 +710,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{661F5711-50C5-4AD1-966A-EEB6DD06A5CB}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.73046875" style="1"/>
-    <col min="2" max="2" width="20.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.19921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.73046875" style="1"/>
+    <col min="1" max="1" width="8.7109375" style="1"/>
+    <col min="2" max="2" width="20.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -713,18 +729,18 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -732,10 +748,10 @@
         <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -746,15 +762,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -765,13 +781,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFC7A54C-E16D-458B-92CE-DB4DE5E21708}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -779,7 +795,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -787,7 +803,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -795,32 +811,32 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -831,14 +847,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4969FD67-2E2F-4920-8A24-9B3F6A7CB976}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.1328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.1328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -849,81 +865,81 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>14</v>
+      <c r="B2" s="4" t="s">
+        <v>46</v>
       </c>
       <c r="C2" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>15</v>
+      <c r="B3" s="4" t="s">
+        <v>47</v>
       </c>
       <c r="C3" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>16</v>
+      <c r="B4" s="4" t="s">
+        <v>48</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>19</v>
+      <c r="B5" s="4" t="s">
+        <v>49</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>20</v>
+      <c r="B6" s="4" t="s">
+        <v>50</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>23</v>
+      <c r="B7" s="4" t="s">
+        <v>51</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>25</v>
+      <c r="B8" s="4" t="s">
+        <v>52</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -934,15 +950,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{139F1479-2E59-4670-8557-FD1A600D9DD9}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.73046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.1328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.1328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.73046875" style="1"/>
+    <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -953,59 +969,59 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>14</v>
+      <c r="B2" s="4" t="s">
+        <v>46</v>
       </c>
       <c r="C2" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>15</v>
+      <c r="B3" s="4" t="s">
+        <v>47</v>
       </c>
       <c r="C3" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>16</v>
+      <c r="B4" s="4" t="s">
+        <v>48</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>19</v>
+      <c r="B5" s="4" t="s">
+        <v>49</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>25</v>
+      <c r="B6" s="4" t="s">
+        <v>52</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1016,15 +1032,15 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{172EB3BB-E440-4D9F-AB45-F40BA5013EFF}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.73046875" style="1"/>
-    <col min="2" max="2" width="20.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.73046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.73046875" style="1"/>
+    <col min="1" max="1" width="8.7109375" style="1"/>
+    <col min="2" max="2" width="20.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1035,7 +1051,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1043,10 +1059,10 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1054,10 +1070,10 @@
         <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -1065,18 +1081,18 @@
         <v>10</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1087,15 +1103,15 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54C0A2D9-C8FF-4F2E-9357-11D1A04AB716}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.73046875" style="1"/>
-    <col min="2" max="2" width="20.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.73046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.73046875" style="1"/>
+    <col min="1" max="1" width="8.7109375" style="1"/>
+    <col min="2" max="2" width="20.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1106,7 +1122,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1114,10 +1130,10 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1125,10 +1141,10 @@
         <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -1136,18 +1152,18 @@
         <v>10</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1158,14 +1174,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F8298A-0165-44BF-9061-10BEE0A93A27}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.265625" customWidth="1"/>
-    <col min="3" max="3" width="100.1328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.28515625" customWidth="1"/>
+    <col min="3" max="3" width="100.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1176,103 +1192,103 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" t="s">
         <v>27</v>
       </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="C6" t="s">
         <v>29</v>
       </c>
-      <c r="C3" t="s">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="C7" t="s">
         <v>31</v>
       </c>
-      <c r="C4" t="s">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="C8" t="s">
         <v>33</v>
       </c>
-      <c r="C5" t="s">
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="C9" t="s">
         <v>35</v>
       </c>
-      <c r="C6" t="s">
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="C10" t="s">
         <v>37</v>
-      </c>
-      <c r="C7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" t="s">
-        <v>41</v>
-      </c>
-      <c r="C9" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" t="s">
-        <v>43</v>
-      </c>
-      <c r="C10" t="s">
-        <v>44</v>
       </c>
     </row>
   </sheetData>
